--- a/server/data/Solar Panel Application 2019-now.xlsx
+++ b/server/data/Solar Panel Application 2019-now.xlsx
@@ -4341,7 +4341,7 @@
       <c r="F72" t="str">
         <v>Roof Mounted Solar PV System - 1,206 sq. ft., 69 x 315 W Modules, System Capacity 21.735</v>
       </c>
-      <c r="G72" t="str">
+      <c r="G72">
         <v>21.735</v>
       </c>
       <c r="H72" t="str">
@@ -5694,8 +5694,8 @@
       <c r="F97" t="str">
         <v>Roof mounted solar PV system - 878sqft 47 Panels x 340W modules System Capacity: 15.98</v>
       </c>
-      <c r="G97" t="str">
-        <v xml:space="preserve"> 15.98</v>
+      <c r="G97">
+        <v>15.98</v>
       </c>
       <c r="H97" t="str">
         <v>Building Commercial</v>
@@ -7441,8 +7441,8 @@
       <c r="F129" t="str">
         <v>Roof Mounted Solar PV System - 706sqft, 38 x 340W Modules, System Capacity: 12.92</v>
       </c>
-      <c r="G129" t="str">
-        <v xml:space="preserve"> 12.92</v>
+      <c r="G129">
+        <v>12.92</v>
       </c>
       <c r="H129" t="str">
         <v>Building Commercial</v>
@@ -7657,8 +7657,8 @@
       <c r="F133" t="str">
         <v>Roof Mounted Solar PV System 5806 sq ft, 272 x 400W Modules, System Capacity: 108.8</v>
       </c>
-      <c r="G133" t="str">
-        <v xml:space="preserve"> 108.8</v>
+      <c r="G133">
+        <v>108.8</v>
       </c>
       <c r="H133" t="str">
         <v>Building Commercial</v>
@@ -7819,8 +7819,8 @@
       <c r="F136" t="str">
         <v>Roof Mounted Solar PV system - 7876 sq ft, 424 x 340W Modules, System Capacity: 144.16</v>
       </c>
-      <c r="G136" t="str">
-        <v xml:space="preserve"> 144.16</v>
+      <c r="G136">
+        <v>144.16</v>
       </c>
       <c r="H136" t="str">
         <v>Building Commercial</v>
@@ -7873,8 +7873,8 @@
       <c r="F137" t="str">
         <v>Roof Mounted Solar PV System - 117 sq ft, 6x350W Modules, System Capacity: 2.1</v>
       </c>
-      <c r="G137" t="str">
-        <v xml:space="preserve"> 2.1</v>
+      <c r="G137">
+        <v>2.1</v>
       </c>
       <c r="H137" t="str">
         <v>Building Residential</v>
@@ -7981,8 +7981,8 @@
       <c r="F139" t="str">
         <v>Roof Mounted Solar PV System - 293 sq ft, 15x350W Modules, System Capacity: 5.25</v>
       </c>
-      <c r="G139" t="str">
-        <v xml:space="preserve"> 5.25</v>
+      <c r="G139">
+        <v>5.25</v>
       </c>
       <c r="H139" t="str">
         <v>Building Residential</v>
@@ -8089,8 +8089,8 @@
       <c r="F141" t="str">
         <v>Roof Mounted Solar PV System - 163 sq ft, 7x430W Modules, System Capacity: 3.01</v>
       </c>
-      <c r="G141" t="str">
-        <v xml:space="preserve"> 3.01</v>
+      <c r="G141">
+        <v>3.01</v>
       </c>
       <c r="H141" t="str">
         <v>Building Residential</v>
@@ -8197,8 +8197,8 @@
       <c r="F143" t="str">
         <v>Roof Mounted Solar PV System - 254 sq ft, 13x350W Modules, System Capacity: 4.55</v>
       </c>
-      <c r="G143" t="str">
-        <v xml:space="preserve"> 4.55</v>
+      <c r="G143">
+        <v>4.55</v>
       </c>
       <c r="H143" t="str">
         <v>Building Residential</v>
@@ -8359,8 +8359,8 @@
       <c r="F146" t="str">
         <v>Ground Mounted Solar PV System - 2508 sq ft, 72 x 340W Modules, System Capacity: 24.48</v>
       </c>
-      <c r="G146" t="str">
-        <v xml:space="preserve"> 24.48</v>
+      <c r="G146">
+        <v>24.48</v>
       </c>
       <c r="H146" t="str">
         <v>Building Residential</v>
@@ -8413,8 +8413,8 @@
       <c r="F147" t="str">
         <v>Roof Mounted Solar PV System - 390 sq ft, 20x350W Modules, System Capacity: 7</v>
       </c>
-      <c r="G147" t="str">
-        <v xml:space="preserve"> 7</v>
+      <c r="G147">
+        <v>7</v>
       </c>
       <c r="H147" t="str">
         <v>Building Residential</v>
@@ -8791,8 +8791,8 @@
       <c r="F154" t="str">
         <v>Roof Mounted Solar PV System - 371 sq ft, 19x360W Modules, System Capacity: 6.84</v>
       </c>
-      <c r="G154" t="str">
-        <v xml:space="preserve"> 6.84</v>
+      <c r="G154">
+        <v>6.84</v>
       </c>
       <c r="H154" t="str">
         <v>Residential</v>
@@ -9169,8 +9169,8 @@
       <c r="F161" t="str">
         <v>Roof Mounted Solar PV System -  215 sq. ft., 11x350W Modules, System Capacity: 3.85</v>
       </c>
-      <c r="G161" t="str">
-        <v xml:space="preserve"> 3.85</v>
+      <c r="G161">
+        <v>3.85</v>
       </c>
       <c r="H161" t="str">
         <v>Residential</v>
@@ -9278,8 +9278,8 @@
       <c r="F163" t="str">
         <v>Roof Mounted Solar PV System - 1089 sq ft, 51 x 400W Modules, System Capacity: 20.4</v>
       </c>
-      <c r="G163" t="str">
-        <v xml:space="preserve"> 20.4</v>
+      <c r="G163">
+        <v>20.4</v>
       </c>
       <c r="H163" t="str">
         <v>Building Residential</v>
@@ -9441,8 +9441,8 @@
       <c r="F166" t="str">
         <v>Roof Mounted Solar PV System - 273 sq ft, 14x360W Modules, System Capacity: 5.04</v>
       </c>
-      <c r="G166" t="str">
-        <v xml:space="preserve"> 5.04</v>
+      <c r="G166">
+        <v>5.04</v>
       </c>
       <c r="H166" t="str">
         <v>Residential</v>
@@ -9550,8 +9550,8 @@
       <c r="F168" t="str">
         <v>Roof Mounted Solar PV System - 371 sq ft, 19x360W Modules, System Capacity: 6.84</v>
       </c>
-      <c r="G168" t="str">
-        <v xml:space="preserve"> 6.84</v>
+      <c r="G168">
+        <v>6.84</v>
       </c>
       <c r="H168" t="str">
         <v>Residential</v>
@@ -10317,8 +10317,8 @@
       <c r="F182" t="str">
         <v>Roof Mounted Solar PV System - 701 sq ft, 30x430W Modules, System Capacity: 12.9</v>
       </c>
-      <c r="G182" t="str">
-        <v xml:space="preserve"> 12.9</v>
+      <c r="G182">
+        <v>12.9</v>
       </c>
       <c r="H182" t="str">
         <v>Residential</v>
@@ -10534,8 +10534,8 @@
       <c r="F186" t="str">
         <v>Roof Mounted Solar PV System - 644 sq ft, 33x360W Modules, System Capacity: 11.88</v>
       </c>
-      <c r="G186" t="str">
-        <v xml:space="preserve"> 11.88</v>
+      <c r="G186">
+        <v>11.88</v>
       </c>
       <c r="H186" t="str">
         <v>Residential</v>
@@ -10645,8 +10645,8 @@
       <c r="F188" t="str">
         <v>Roof Mounted Solar PV System - 312 sq ft,  16x360W Modules, System Capacity: 5.76</v>
       </c>
-      <c r="G188" t="str">
-        <v xml:space="preserve"> 5.76</v>
+      <c r="G188">
+        <v>5.76</v>
       </c>
       <c r="H188" t="str">
         <v>Residential</v>
@@ -10699,8 +10699,8 @@
       <c r="F189" t="str">
         <v>Roof Mounted Solar PV System - 527 sq ft, 27x360W Modules, System Capacity: 9.72</v>
       </c>
-      <c r="G189" t="str">
-        <v xml:space="preserve"> 9.72</v>
+      <c r="G189">
+        <v>9.72</v>
       </c>
       <c r="H189" t="str">
         <v>Residential</v>
@@ -10753,8 +10753,8 @@
       <c r="F190" t="str">
         <v>Roof Mounted Solar PV System - 371 sq ft, 19x360W Modules, System Capacity: 6.84</v>
       </c>
-      <c r="G190" t="str">
-        <v xml:space="preserve"> 6.84</v>
+      <c r="G190">
+        <v>6.84</v>
       </c>
       <c r="H190" t="str">
         <v>Residential</v>
@@ -10807,8 +10807,8 @@
       <c r="F191" t="str">
         <v>Roof Mounted Solar PV System - 566 sq ft., 29x360W Modules, System Capacity: 10.44</v>
       </c>
-      <c r="G191" t="str">
-        <v xml:space="preserve"> 10.44</v>
+      <c r="G191">
+        <v>10.44</v>
       </c>
       <c r="H191" t="str">
         <v>Residential</v>
@@ -10915,8 +10915,8 @@
       <c r="F193" t="str">
         <v>Roof Mounted Solar PV System - 215 sq ft, 11x360W Modules and System Capacity: 3.96</v>
       </c>
-      <c r="G193" t="str">
-        <v xml:space="preserve"> 3.96</v>
+      <c r="G193">
+        <v>3.96</v>
       </c>
       <c r="H193" t="str">
         <v>Residential</v>
@@ -11077,8 +11077,8 @@
       <c r="F196" t="str">
         <v>Roof Mounted Solar PV System 2803 sq ft, 120x430W Modules, System Capacity: 51.6</v>
       </c>
-      <c r="G196" t="str">
-        <v xml:space="preserve"> 51.6</v>
+      <c r="G196">
+        <v>51.6</v>
       </c>
       <c r="H196" t="str">
         <v>Building Commercial</v>
@@ -11131,8 +11131,8 @@
       <c r="F197" t="str">
         <v>Roof Mounted Solar PV System - 546 sq ft, 28x360W Modules, System Capacity: 10.08</v>
       </c>
-      <c r="G197" t="str">
-        <v xml:space="preserve"> 10.08</v>
+      <c r="G197">
+        <v>10.08</v>
       </c>
       <c r="H197" t="str">
         <v>Residential</v>
@@ -11185,8 +11185,8 @@
       <c r="F198" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 15 panels, 293 sq ft, 360W Modules, System Capacity: 5.4 </v>
       </c>
-      <c r="G198" t="str">
-        <v xml:space="preserve"> 5.4 </v>
+      <c r="G198">
+        <v>5.4</v>
       </c>
       <c r="H198" t="str">
         <v>Residential</v>
@@ -11239,8 +11239,8 @@
       <c r="F199" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 11 panels, 215 sq ft, 360W Modules, System Capacity: 3.96 </v>
       </c>
-      <c r="G199" t="str">
-        <v xml:space="preserve"> 3.96 </v>
+      <c r="G199">
+        <v>3.96</v>
       </c>
       <c r="H199" t="str">
         <v>Residential</v>
@@ -11347,8 +11347,8 @@
       <c r="F201" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 293 sq ft, 360W Modules, System Capacity: 5.4 </v>
       </c>
-      <c r="G201" t="str">
-        <v xml:space="preserve"> 5.4 </v>
+      <c r="G201">
+        <v>5.4</v>
       </c>
       <c r="H201" t="str">
         <v>Residential</v>
@@ -11401,8 +11401,8 @@
       <c r="F202" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 527 sq ft,  27x360W Modules, System Capacity: 9.72 </v>
       </c>
-      <c r="G202" t="str">
-        <v xml:space="preserve"> 9.72 </v>
+      <c r="G202">
+        <v>9.72</v>
       </c>
       <c r="H202" t="str">
         <v>Residential</v>
@@ -11674,8 +11674,8 @@
       <c r="F207" t="str">
         <v>Roof Mounted solar PV system - 273 sq ft, 14 x 360W Modules, System Capacity: 5.04</v>
       </c>
-      <c r="G207" t="str">
-        <v xml:space="preserve"> 5.04</v>
+      <c r="G207">
+        <v>5.04</v>
       </c>
       <c r="H207" t="str">
         <v>Residential</v>
@@ -11728,8 +11728,8 @@
       <c r="F208" t="str">
         <v>Roof Mounted Solar PV System - 471 sq ft, 24 x 365W Modules, System Capacity: 8.76</v>
       </c>
-      <c r="G208" t="str">
-        <v xml:space="preserve"> 8.76</v>
+      <c r="G208">
+        <v>8.76</v>
       </c>
       <c r="H208" t="str">
         <v>Residential</v>
@@ -11782,8 +11782,8 @@
       <c r="F209" t="str">
         <v>Roof Mounted Solar PV System - 314 sq ft, 16 Modules, 365W Modules, System Capacity: 5.84</v>
       </c>
-      <c r="G209" t="str">
-        <v xml:space="preserve"> 5.84</v>
+      <c r="G209">
+        <v>5.84</v>
       </c>
       <c r="H209" t="str">
         <v>Residential</v>
@@ -11836,8 +11836,8 @@
       <c r="F210" t="str">
         <v>Roof Mounted Solar PV System - 432 sq ft, 22 x 365W Modules, System Capacity: 8.03</v>
       </c>
-      <c r="G210" t="str">
-        <v xml:space="preserve"> 8.03</v>
+      <c r="G210">
+        <v>8.03</v>
       </c>
       <c r="H210" t="str">
         <v>Residential</v>
@@ -11890,8 +11890,8 @@
       <c r="F211" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 546 sq ft, 28 Modules, 360W Modules, System Capacity: 10.08 </v>
       </c>
-      <c r="G211" t="str">
-        <v xml:space="preserve"> 10.08 </v>
+      <c r="G211">
+        <v>10.08</v>
       </c>
       <c r="H211" t="str">
         <v>Residential</v>
@@ -11998,8 +11998,8 @@
       <c r="F213" t="str">
         <v>Roof Mounted Solar PV System - 351 sq ft, 18x360W Modules, System Capacity: 6.48</v>
       </c>
-      <c r="G213" t="str">
-        <v xml:space="preserve"> 6.48</v>
+      <c r="G213">
+        <v>6.48</v>
       </c>
       <c r="H213" t="str">
         <v>Residential</v>
@@ -12052,8 +12052,8 @@
       <c r="F214" t="str">
         <v>Roof Mounted Solar PV System - 468 sq ft, 24x360W Modules, System Capacity: 8.64</v>
       </c>
-      <c r="G214" t="str">
-        <v xml:space="preserve"> 8.64</v>
+      <c r="G214">
+        <v>8.64</v>
       </c>
       <c r="H214" t="str">
         <v>Residential</v>
@@ -12106,8 +12106,8 @@
       <c r="F215" t="str">
         <v>Roof Mounted Solar PV System - 157 sq ft, 8 Modules, 365W Modules, System Capacity: 2.92</v>
       </c>
-      <c r="G215" t="str">
-        <v xml:space="preserve"> 2.92</v>
+      <c r="G215">
+        <v>2.92</v>
       </c>
       <c r="H215" t="str">
         <v>Residential</v>
@@ -12160,8 +12160,8 @@
       <c r="F216" t="str">
         <v>Roof Mounted Solar PV System -507 sq ft,  26x360W Modules, System Capacity: 9.36</v>
       </c>
-      <c r="G216" t="str">
-        <v xml:space="preserve"> 9.36</v>
+      <c r="G216">
+        <v>9.36</v>
       </c>
       <c r="H216" t="str">
         <v>Residential</v>
@@ -12322,8 +12322,8 @@
       <c r="F219" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 663 sq ft, 34x360W Modules, System Capacity:12.24 </v>
       </c>
-      <c r="G219" t="str">
-        <v xml:space="preserve">12.24 </v>
+      <c r="G219">
+        <v>12.24</v>
       </c>
       <c r="H219" t="str">
         <v>Residential</v>
@@ -12653,8 +12653,8 @@
       <c r="F225" t="str">
         <v>Roof Mounted Solar PV System - 275 sq ft, 14x365W Modules, System Capacity: 5.11</v>
       </c>
-      <c r="G225" t="str">
-        <v xml:space="preserve"> 5.11</v>
+      <c r="G225">
+        <v>5.11</v>
       </c>
       <c r="H225" t="str">
         <v>Residential</v>
@@ -12923,8 +12923,8 @@
       <c r="F230" t="str">
         <v>Roof Mounted Solar PV System - 761 sq ft, 39x360W Modules, System Capacity: 14.04</v>
       </c>
-      <c r="G230" t="str">
-        <v xml:space="preserve"> 14.04</v>
+      <c r="G230">
+        <v>14.04</v>
       </c>
       <c r="H230" t="str">
         <v>Residential</v>
@@ -13086,8 +13086,8 @@
       <c r="F233" t="str">
         <v>Roof Mounted Solar PV System - 254 sq ft, 13 x 360W Modules, System Capacity: 4.68</v>
       </c>
-      <c r="G233" t="str">
-        <v xml:space="preserve"> 4.68</v>
+      <c r="G233">
+        <v>4.68</v>
       </c>
       <c r="H233" t="str">
         <v>Residential</v>
@@ -13140,8 +13140,8 @@
       <c r="F234" t="str">
         <v>Roof Mounted Solar PV System - 654 sq ft, 28x430W Modules, System Capacity: 12.04</v>
       </c>
-      <c r="G234" t="str">
-        <v xml:space="preserve"> 12.04</v>
+      <c r="G234">
+        <v>12.04</v>
       </c>
       <c r="H234" t="str">
         <v>Residential</v>
@@ -13302,8 +13302,8 @@
       <c r="F237" t="str">
         <v>Roof Mounted Solar PV System - 702 sq ft, 36x360W Modules, System Capacity: 12.96</v>
       </c>
-      <c r="G237" t="str">
-        <v xml:space="preserve"> 12.96</v>
+      <c r="G237">
+        <v>12.96</v>
       </c>
       <c r="H237" t="str">
         <v>Residential</v>
@@ -13356,8 +13356,8 @@
       <c r="F238" t="str">
         <v>Roof Mounted Solar PV System - 176 sq ft, 9x360W Modules, System Capacity: 3.24</v>
       </c>
-      <c r="G238" t="str">
-        <v xml:space="preserve"> 3.24</v>
+      <c r="G238">
+        <v>3.24</v>
       </c>
       <c r="H238" t="str">
         <v>Residential</v>
@@ -13572,8 +13572,8 @@
       <c r="F242" t="str">
         <v>Roof Mounted Solar PV System - 550 sq ft, 28x365W Modules, System Capacity: 10.22</v>
       </c>
-      <c r="G242" t="str">
-        <v xml:space="preserve"> 10.22</v>
+      <c r="G242">
+        <v>10.22</v>
       </c>
       <c r="H242" t="str">
         <v>Residential</v>
@@ -13680,8 +13680,8 @@
       <c r="F244" t="str">
         <v>Roof Mounted Solar PV System - 215 sq ft, 11x360W Modules, System Capacity: 3.96</v>
       </c>
-      <c r="G244" t="str">
-        <v xml:space="preserve"> 3.96</v>
+      <c r="G244">
+        <v>3.96</v>
       </c>
       <c r="H244" t="str">
         <v>Residential</v>
@@ -13734,8 +13734,8 @@
       <c r="F245" t="str">
         <v>Roof Mounted Solar PV System - 254 sq ft, 13x360W Modules, System Capacity: 4.68</v>
       </c>
-      <c r="G245" t="str">
-        <v xml:space="preserve"> 4.68</v>
+      <c r="G245">
+        <v>4.68</v>
       </c>
       <c r="H245" t="str">
         <v>Residential</v>
@@ -13788,8 +13788,8 @@
       <c r="F246" t="str">
         <v>Roof Mounted Solar PV System - 351 sq ft, 18x360W Modules, System Capacity: 6.48</v>
       </c>
-      <c r="G246" t="str">
-        <v xml:space="preserve"> 6.48</v>
+      <c r="G246">
+        <v>6.48</v>
       </c>
       <c r="H246" t="str">
         <v>Residential</v>
@@ -14005,8 +14005,8 @@
       <c r="F250" t="str">
         <v>Roof Mounted Solar PV System - 412 sq ft, 21x365W Modules, System Capacity: 7.665</v>
       </c>
-      <c r="G250" t="str">
-        <v xml:space="preserve"> 7.665</v>
+      <c r="G250">
+        <v>7.665</v>
       </c>
       <c r="H250" t="str">
         <v>Residential</v>
@@ -14279,8 +14279,8 @@
       <c r="F255" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 410 sq ft, 21x360W Modules, System Capacity: 7.56 </v>
       </c>
-      <c r="G255" t="str">
-        <v xml:space="preserve"> 7.56 </v>
+      <c r="G255">
+        <v>7.56</v>
       </c>
       <c r="H255" t="str">
         <v>Building Residential</v>
@@ -14441,8 +14441,8 @@
       <c r="F258" t="str">
         <v>Roof Mounted Solar PV System - 371 sq ft., 19x360W Modules, System Capacity: 6.84</v>
       </c>
-      <c r="G258" t="str">
-        <v xml:space="preserve"> 6.84</v>
+      <c r="G258">
+        <v>6.84</v>
       </c>
       <c r="H258" t="str">
         <v>Residential</v>
@@ -14658,8 +14658,8 @@
       <c r="F262" t="str">
         <v>Roof Mounted Solar PV System - 236 sq ft, 12x365W Modules, System Capacity: 4.38</v>
       </c>
-      <c r="G262" t="str">
-        <v xml:space="preserve"> 4.38</v>
+      <c r="G262">
+        <v>4.38</v>
       </c>
       <c r="H262" t="str">
         <v>Residential</v>
@@ -14766,8 +14766,8 @@
       <c r="F264" t="str">
         <v>Roof Mounted Solar PV System - 118 sq ft, 6x365W Modules, System Capacity: 2.19</v>
       </c>
-      <c r="G264" t="str">
-        <v xml:space="preserve"> 2.19</v>
+      <c r="G264">
+        <v>2.19</v>
       </c>
       <c r="H264" t="str">
         <v>Residential</v>
@@ -14928,8 +14928,8 @@
       <c r="F267" t="str">
         <v>Roof Mounted Solar PV System - 98 sq ft, 5x360W Modules, System Capacity: 1.8</v>
       </c>
-      <c r="G267" t="str">
-        <v xml:space="preserve"> 1.8</v>
+      <c r="G267">
+        <v>1.8</v>
       </c>
       <c r="H267" t="str">
         <v>Residential</v>
@@ -15252,8 +15252,8 @@
       <c r="F273" t="str">
         <v>Roof Mounted Solar PV System - 452 sq ft, 23x365W Modules, System Capacity: 8.395</v>
       </c>
-      <c r="G273" t="str">
-        <v xml:space="preserve"> 8.395</v>
+      <c r="G273">
+        <v>8.395</v>
       </c>
       <c r="H273" t="str">
         <v>Residential</v>
@@ -15415,8 +15415,8 @@
       <c r="F276" t="str">
         <v>Roof Mounted Solar PV System - 254 sq ft, 13x360W Modules, System Capacity: 4.68</v>
       </c>
-      <c r="G276" t="str">
-        <v xml:space="preserve"> 4.68</v>
+      <c r="G276">
+        <v>4.68</v>
       </c>
       <c r="H276" t="str">
         <v>Residential</v>
@@ -15469,8 +15469,8 @@
       <c r="F277" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 176 sq ft, 9x360W Modules, System Capacity: 3.24 </v>
       </c>
-      <c r="G277" t="str">
-        <v xml:space="preserve"> 3.24 </v>
+      <c r="G277">
+        <v>3.24</v>
       </c>
       <c r="H277" t="str">
         <v>Residential</v>
@@ -15688,8 +15688,8 @@
       <c r="F281" t="str">
         <v>Roof Mounted Solar PV System - 351 sq ft, 18 x 360W Modules, System Capacity: 6.48</v>
       </c>
-      <c r="G281" t="str">
-        <v xml:space="preserve"> 6.48</v>
+      <c r="G281">
+        <v>6.48</v>
       </c>
       <c r="H281" t="str">
         <v>Residential</v>
@@ -15742,8 +15742,8 @@
       <c r="F282" t="str">
         <v>Roof Mounted Solar PV System - 393 sq ft, 20 Panels, 365W Modules, System Capacity: 7.3</v>
       </c>
-      <c r="G282" t="str">
-        <v xml:space="preserve"> 7.3</v>
+      <c r="G282">
+        <v>7.3</v>
       </c>
       <c r="H282" t="str">
         <v>Residential</v>
@@ -16176,8 +16176,8 @@
       <c r="F290" t="str">
         <v xml:space="preserve">Solar PV System: 13 panels @ 360 W/panel; Total Area 254 sq ft; Total System Capacity 4.68 </v>
       </c>
-      <c r="G290" t="str">
-        <v xml:space="preserve">4.68 </v>
+      <c r="G290">
+        <v>4.68</v>
       </c>
       <c r="H290" t="str">
         <v>Residential Revision</v>
@@ -16338,8 +16338,8 @@
       <c r="F293" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 312 sq ft, 16x360W Modules, System Capacity: 5.76 </v>
       </c>
-      <c r="G293" t="str">
-        <v xml:space="preserve"> 5.76 </v>
+      <c r="G293">
+        <v>5.76</v>
       </c>
       <c r="H293" t="str">
         <v>Residential</v>
@@ -16392,8 +16392,8 @@
       <c r="F294" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 293 sq ft, 15x360W Modules, System Capacity: 5.4 </v>
       </c>
-      <c r="G294" t="str">
-        <v xml:space="preserve"> 5.4 </v>
+      <c r="G294">
+        <v>5.4</v>
       </c>
       <c r="H294" t="str">
         <v>Residential</v>
@@ -17100,8 +17100,8 @@
       <c r="F307" t="str">
         <v>Roof Mounted Solar PV System - 412sqft, 21 x Aptos 365W Modules, System Capacity: 7.665</v>
       </c>
-      <c r="G307" t="str">
-        <v xml:space="preserve"> 7.665</v>
+      <c r="G307">
+        <v>7.665</v>
       </c>
       <c r="H307" t="str">
         <v>Residential</v>
@@ -17859,8 +17859,8 @@
       <c r="F321" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 334 sq ft, 17 Aptos 370W Modules, System Capacity: 6.29 </v>
       </c>
-      <c r="G321" t="str">
-        <v xml:space="preserve"> 6.29 </v>
+      <c r="G321">
+        <v>6.29</v>
       </c>
       <c r="H321" t="str">
         <v>Residential</v>
@@ -17913,8 +17913,8 @@
       <c r="F322" t="str">
         <v>Roof Mounted Solar PV System - 196sqft,  10x365W modules, System Capacity: 3.65</v>
       </c>
-      <c r="G322" t="str">
-        <v xml:space="preserve"> 3.65</v>
+      <c r="G322">
+        <v>3.65</v>
       </c>
       <c r="H322" t="str">
         <v>Residential</v>
@@ -18021,8 +18021,8 @@
       <c r="F324" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 468 sq ft, 24 x 360W Modules, System Capacity: 8.64 </v>
       </c>
-      <c r="G324" t="str">
-        <v xml:space="preserve"> 8.64 </v>
+      <c r="G324">
+        <v>8.64</v>
       </c>
       <c r="H324" t="str">
         <v>Residential</v>
@@ -18129,8 +18129,8 @@
       <c r="F326" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 275 sq ft, 14 x 365W Modules, System Capacity: 5.11 </v>
       </c>
-      <c r="G326" t="str">
-        <v xml:space="preserve"> 5.11 </v>
+      <c r="G326">
+        <v>5.11</v>
       </c>
       <c r="H326" t="str">
         <v>Residential</v>
@@ -18509,8 +18509,8 @@
       <c r="F333" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 491 sq ft, 25 X 365W Modules, System Capacity: 9.125 </v>
       </c>
-      <c r="G333" t="str">
-        <v xml:space="preserve"> 9.125 </v>
+      <c r="G333">
+        <v>9.125</v>
       </c>
       <c r="H333" t="str">
         <v>Residential</v>
@@ -18833,8 +18833,8 @@
       <c r="F339" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 511 sq ft, 26 x 365W Modules, System Capacity: 9.49 </v>
       </c>
-      <c r="G339" t="str">
-        <v xml:space="preserve"> 9.49 </v>
+      <c r="G339">
+        <v>9.49</v>
       </c>
       <c r="H339" t="str">
         <v>Residential</v>
@@ -18887,8 +18887,8 @@
       <c r="F340" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 373 sq ft, 19 x 365W Modules, System Capacity: 6.935 </v>
       </c>
-      <c r="G340" t="str">
-        <v xml:space="preserve"> 6.935 </v>
+      <c r="G340">
+        <v>6.935</v>
       </c>
       <c r="H340" t="str">
         <v>Residential</v>
@@ -18941,8 +18941,8 @@
       <c r="F341" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 628 sq ft, 32 x 365W Modules, System Capacity: 11.68  </v>
       </c>
-      <c r="G341" t="str">
-        <v xml:space="preserve"> 11.68  </v>
+      <c r="G341">
+        <v>11.68</v>
       </c>
       <c r="H341" t="str">
         <v>Residential</v>
@@ -19049,8 +19049,8 @@
       <c r="F343" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 275 sq ft, 14 x 365W Modules, System Capacity: 5.11 </v>
       </c>
-      <c r="G343" t="str">
-        <v xml:space="preserve"> 5.11 </v>
+      <c r="G343">
+        <v>5.11</v>
       </c>
       <c r="H343" t="str">
         <v>Residential</v>
@@ -19373,8 +19373,8 @@
       <c r="F349" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 78 sq ft, 4 x 360W Modules, System Capacity: 1.44 </v>
       </c>
-      <c r="G349" t="str">
-        <v xml:space="preserve"> 1.44 </v>
+      <c r="G349">
+        <v>1.44</v>
       </c>
       <c r="H349" t="str">
         <v>Residential</v>
@@ -19915,8 +19915,8 @@
       <c r="F359" t="str">
         <v>Roof Mounted Solar PV System - 354 sq ft, 18 X 370W Modules, System Capacity: 6.66</v>
       </c>
-      <c r="G359" t="str">
-        <v xml:space="preserve"> 6.66</v>
+      <c r="G359">
+        <v>6.66</v>
       </c>
       <c r="H359" t="str">
         <v>Residential</v>
@@ -20294,8 +20294,8 @@
       <c r="F366" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 164 sq ft, 7 x 440W Modules, System Capacity: 3.08 </v>
       </c>
-      <c r="G366" t="str">
-        <v xml:space="preserve"> 3.08 </v>
+      <c r="G366">
+        <v>3.08</v>
       </c>
       <c r="H366" t="str">
         <v>Residential</v>
@@ -20619,8 +20619,8 @@
         <v xml:space="preserve">New Solar Panel Installation with Timber Pergola and Block Work to Existing Boundary Wall 16 Panels @ 370W/ Panel; Total Area 314 sq ft; Total Output 5.92_x000d_
 Annual Output h:7488 h.  Total AC Output:  4.64</v>
       </c>
-      <c r="G372" t="str">
-        <v xml:space="preserve">  4.64</v>
+      <c r="G372">
+        <v>4.64</v>
       </c>
       <c r="H372" t="str">
         <v>Residential</v>
@@ -20728,8 +20728,8 @@
       <c r="F374" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 275 sq ft,14 x 370W Modules, System Capacity: 5.18 </v>
       </c>
-      <c r="G374" t="str">
-        <v xml:space="preserve"> 5.18 </v>
+      <c r="G374">
+        <v>5.18</v>
       </c>
       <c r="H374" t="str">
         <v>Residential</v>
@@ -20782,8 +20782,8 @@
       <c r="F375" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 530 sq ft, 27 X 370W Modules, System Capacity: 9.99 </v>
       </c>
-      <c r="G375" t="str">
-        <v xml:space="preserve"> 9.99 </v>
+      <c r="G375">
+        <v>9.99</v>
       </c>
       <c r="H375" t="str">
         <v>Residential</v>
@@ -20836,8 +20836,8 @@
       <c r="F376" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 177 sq ft.  9 x 370W Modules.  System Capacity: 3.33 </v>
       </c>
-      <c r="G376" t="str">
-        <v xml:space="preserve"> 3.33 </v>
+      <c r="G376">
+        <v>3.33</v>
       </c>
       <c r="H376" t="str">
         <v>Residential</v>
@@ -20944,8 +20944,8 @@
       <c r="F378" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System -334 sq ft, 17 X 370W Modules, System Capacity: 6.29 </v>
       </c>
-      <c r="G378" t="str">
-        <v xml:space="preserve"> 6.29 </v>
+      <c r="G378">
+        <v>6.29</v>
       </c>
       <c r="H378" t="str">
         <v>Residential</v>
@@ -21652,8 +21652,8 @@
       <c r="F391" t="str">
         <v>Roof Mounted Solar PV System - 255 sq ft,13 x 370W Modules System Capacity: 4.81</v>
       </c>
-      <c r="G391" t="str">
-        <v xml:space="preserve"> 4.81</v>
+      <c r="G391">
+        <v>4.81</v>
       </c>
       <c r="H391" t="str">
         <v>Residential</v>
@@ -21924,8 +21924,8 @@
       <c r="F396" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 295 sq ft, 15 X 370W Modules, System Capacity: 5.55 </v>
       </c>
-      <c r="G396" t="str">
-        <v xml:space="preserve"> 5.55 </v>
+      <c r="G396">
+        <v>5.55</v>
       </c>
       <c r="H396" t="str">
         <v>Residential</v>
@@ -22096,8 +22096,8 @@
       <c r="F399" t="str">
         <v>Roof Mounted Solar PV System - 527 sq ft,27 x 360W Modules, System Capacity: 9.72</v>
       </c>
-      <c r="G399" t="str">
-        <v xml:space="preserve"> 9.72</v>
+      <c r="G399">
+        <v>9.72</v>
       </c>
       <c r="H399" t="str">
         <v>Residential</v>
@@ -22150,8 +22150,8 @@
       <c r="F400" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 471 sq ft, 24 X 370W Modules, System Capacity: 8.88 </v>
       </c>
-      <c r="G400" t="str">
-        <v xml:space="preserve"> 8.88 </v>
+      <c r="G400">
+        <v>8.88</v>
       </c>
       <c r="H400" t="str">
         <v>Residential</v>
@@ -22312,8 +22312,8 @@
       <c r="F403" t="str">
         <v>Roof Mounted Solar PV System - 354 sq ft., 18 x 370W Modules, System Capacity: 6.66</v>
       </c>
-      <c r="G403" t="str">
-        <v xml:space="preserve"> 6.66</v>
+      <c r="G403">
+        <v>6.66</v>
       </c>
       <c r="H403" t="str">
         <v>Residential</v>
@@ -22474,8 +22474,8 @@
       <c r="F406" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 393 sq ft., 20 X 370W Modules, System Capacity: 7.4 </v>
       </c>
-      <c r="G406" t="str">
-        <v xml:space="preserve"> 7.4 </v>
+      <c r="G406">
+        <v>7.4</v>
       </c>
       <c r="H406" t="str">
         <v>Residential</v>
@@ -22528,8 +22528,8 @@
       <c r="F407" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 570 sq ft., 29 X 370W Modules, System Capacity: 10.73 </v>
       </c>
-      <c r="G407" t="str">
-        <v xml:space="preserve"> 10.73 </v>
+      <c r="G407">
+        <v>10.73</v>
       </c>
       <c r="H407" t="str">
         <v>Residential</v>
@@ -22744,8 +22744,8 @@
       <c r="F411" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 393 sq ft., 20 x 370W Modules, System Capacity: 7.4 </v>
       </c>
-      <c r="G411" t="str">
-        <v xml:space="preserve"> 7.4 </v>
+      <c r="G411">
+        <v>7.4</v>
       </c>
       <c r="H411" t="str">
         <v>Residential</v>
@@ -22906,8 +22906,8 @@
       <c r="F414" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 275 sq ft,14 x 370W Modules, System Capacity: 5.18 </v>
       </c>
-      <c r="G414" t="str">
-        <v xml:space="preserve"> 5.18 </v>
+      <c r="G414">
+        <v>5.18</v>
       </c>
       <c r="H414" t="str">
         <v>Residential</v>
@@ -22960,8 +22960,8 @@
       <c r="F415" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 275 sq ft.,  14 X Aptos 370W Modules, System Capacity: 5.18 </v>
       </c>
-      <c r="G415" t="str">
-        <v xml:space="preserve"> 5.18 </v>
+      <c r="G415">
+        <v>5.18</v>
       </c>
       <c r="H415" t="str">
         <v>Residential</v>
@@ -23014,8 +23014,8 @@
       <c r="F416" t="str">
         <v>Roof Mounted Solar PV System - 412 sq ft., 21 X 370W Modules, System Capacity: 7.77</v>
       </c>
-      <c r="G416" t="str">
-        <v xml:space="preserve"> 7.77</v>
+      <c r="G416">
+        <v>7.77</v>
       </c>
       <c r="H416" t="str">
         <v>Residential</v>
@@ -23068,8 +23068,8 @@
       <c r="F417" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 275 sq ft, 14 X 370W Modules, System Capacity: 5.18 </v>
       </c>
-      <c r="G417" t="str">
-        <v xml:space="preserve"> 5.18 </v>
+      <c r="G417">
+        <v>5.18</v>
       </c>
       <c r="H417" t="str">
         <v>Residential</v>
@@ -23176,8 +23176,8 @@
       <c r="F419" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 314 sq ft, 16x365W Modules, System Capacity: 5.84 </v>
       </c>
-      <c r="G419" t="str">
-        <v xml:space="preserve"> 5.84 </v>
+      <c r="G419">
+        <v>5.84</v>
       </c>
       <c r="H419" t="str">
         <v>Building Residential</v>
@@ -23501,8 +23501,8 @@
       <c r="F425" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 334 sq ft, 17x370W Modules, System Capacity: 6.29 </v>
       </c>
-      <c r="G425" t="str">
-        <v xml:space="preserve"> 6.29 </v>
+      <c r="G425">
+        <v>6.29</v>
       </c>
       <c r="H425" t="str">
         <v>Residential</v>
@@ -24044,8 +24044,8 @@
       <c r="F435" t="str">
         <v>Roof Mounted Solar PV System - 281 sq ft, 12x440W Modules, System Capacity: 5.28</v>
       </c>
-      <c r="G435" t="str">
-        <v xml:space="preserve"> 5.28</v>
+      <c r="G435">
+        <v>5.28</v>
       </c>
       <c r="H435" t="str">
         <v>Building Commercial</v>
@@ -24098,8 +24098,8 @@
       <c r="F436" t="str">
         <v>Roof Mounted Solar PV System - 373 sq ft, 19x370W Modules, System Capacity: 7.03</v>
       </c>
-      <c r="G436" t="str">
-        <v xml:space="preserve"> 7.03</v>
+      <c r="G436">
+        <v>7.03</v>
       </c>
       <c r="H436" t="str">
         <v>Residential</v>
@@ -24152,8 +24152,8 @@
       <c r="F437" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 550 sq ft, 28x370W Modules, System Capacity: 10.36 </v>
       </c>
-      <c r="G437" t="str">
-        <v xml:space="preserve"> 10.36 </v>
+      <c r="G437">
+        <v>10.36</v>
       </c>
       <c r="H437" t="str">
         <v>Residential</v>
@@ -24206,8 +24206,8 @@
       <c r="F438" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 393 sq ft, 20 x 370W Modules, System Capacity: 7.4 </v>
       </c>
-      <c r="G438" t="str">
-        <v xml:space="preserve"> 7.4 </v>
+      <c r="G438">
+        <v>7.4</v>
       </c>
       <c r="H438" t="str">
         <v>Residential</v>
@@ -24422,8 +24422,8 @@
       <c r="F442" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 314 sq ft, 16x370W Modules, System Capacity: 5.92 </v>
       </c>
-      <c r="G442" t="str">
-        <v xml:space="preserve"> 5.92 </v>
+      <c r="G442">
+        <v>5.92</v>
       </c>
       <c r="H442" t="str">
         <v>Residential</v>
@@ -24530,8 +24530,8 @@
       <c r="F444" t="str">
         <v>Roof Mounted Solar PV System - 314 sq ft, 16x370W Modules, System Capacity: 5.92</v>
       </c>
-      <c r="G444" t="str">
-        <v xml:space="preserve"> 5.92</v>
+      <c r="G444">
+        <v>5.92</v>
       </c>
       <c r="H444" t="str">
         <v>Residential</v>
@@ -24584,8 +24584,8 @@
       <c r="F445" t="str">
         <v>Roof Mounted Solar PV System - 255 sq ft, 13x370W Modules, System Capacity: 4.81</v>
       </c>
-      <c r="G445" t="str">
-        <v xml:space="preserve"> 4.81</v>
+      <c r="G445">
+        <v>4.81</v>
       </c>
       <c r="H445" t="str">
         <v>Residential</v>
@@ -24638,8 +24638,8 @@
       <c r="F446" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 177 sq ft, 9x365W Modules, System Capacity: 3.285 </v>
       </c>
-      <c r="G446" t="str">
-        <v xml:space="preserve"> 3.285 </v>
+      <c r="G446">
+        <v>3.285</v>
       </c>
       <c r="H446" t="str">
         <v>Building Residential</v>
@@ -24748,8 +24748,8 @@
       <c r="F448" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 608 sq ft, 31x370W Modules, System Capacity: 11.47 </v>
       </c>
-      <c r="G448" t="str">
-        <v xml:space="preserve"> 11.47 </v>
+      <c r="G448">
+        <v>11.47</v>
       </c>
       <c r="H448" t="str">
         <v>Residential</v>
@@ -25020,8 +25020,8 @@
       <c r="F453" t="str">
         <v>Roof Mounted Solar PV System - 314 sq ft, 16x370W Modules, System Capacity: 5.92</v>
       </c>
-      <c r="G453" t="str">
-        <v xml:space="preserve"> 5.92</v>
+      <c r="G453">
+        <v>5.92</v>
       </c>
       <c r="H453" t="str">
         <v>Residential</v>
@@ -25236,8 +25236,8 @@
       <c r="F457" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 216 sq ft, 11x370W Modules, System Capacity: 4.07 </v>
       </c>
-      <c r="G457" t="str">
-        <v xml:space="preserve"> 4.07 </v>
+      <c r="G457">
+        <v>4.07</v>
       </c>
       <c r="H457" t="str">
         <v>Residential</v>
@@ -25290,8 +25290,8 @@
       <c r="F458" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 137 sq ft,  7 x 370W Modules, System Capacity: 2.59 </v>
       </c>
-      <c r="G458" t="str">
-        <v xml:space="preserve"> 2.59 </v>
+      <c r="G458">
+        <v>2.59</v>
       </c>
       <c r="H458" t="str">
         <v>Residential</v>
@@ -25344,8 +25344,8 @@
       <c r="F459" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 530 sq ft, 27x370W Module, System Capacity: 9.99 </v>
       </c>
-      <c r="G459" t="str">
-        <v xml:space="preserve"> 9.99 </v>
+      <c r="G459">
+        <v>9.99</v>
       </c>
       <c r="H459" t="str">
         <v>Residential</v>
@@ -25398,8 +25398,8 @@
       <c r="F460" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 471 sq ft, 24x370W Modules, System Capacity: 8.88 </v>
       </c>
-      <c r="G460" t="str">
-        <v xml:space="preserve"> 8.88 </v>
+      <c r="G460">
+        <v>8.88</v>
       </c>
       <c r="H460" t="str">
         <v>Building Residential</v>
@@ -25506,8 +25506,8 @@
       <c r="F462" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 215 sq ft, 11x370W Modules, System Capacity: 3.19 </v>
       </c>
-      <c r="G462" t="str">
-        <v xml:space="preserve"> 3.19 </v>
+      <c r="G462">
+        <v>3.19</v>
       </c>
       <c r="H462" t="str">
         <v>Residential</v>
@@ -25560,8 +25560,8 @@
       <c r="F463" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 727 sq ft, 37x370W Modules, System Capacity: 13.69 </v>
       </c>
-      <c r="G463" t="str">
-        <v xml:space="preserve"> 13.69 </v>
+      <c r="G463">
+        <v>13.69</v>
       </c>
       <c r="H463" t="str">
         <v>Residential</v>
@@ -25722,8 +25722,8 @@
       <c r="F466" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 332 sq ft, 17x370W Modules, System Capacity: 6.29 </v>
       </c>
-      <c r="G466" t="str">
-        <v xml:space="preserve"> 6.29 </v>
+      <c r="G466">
+        <v>6.29</v>
       </c>
       <c r="H466" t="str">
         <v>Residential</v>
@@ -25776,8 +25776,8 @@
       <c r="F467" t="str">
         <v xml:space="preserve">Addition to existing Roof Mounted Solar PV System - 196 sq ft, 10x370W Modules, System Capacity: 3.7 </v>
       </c>
-      <c r="G467" t="str">
-        <v xml:space="preserve"> 3.7 </v>
+      <c r="G467">
+        <v>3.7</v>
       </c>
       <c r="H467" t="str">
         <v>Residential</v>
@@ -26154,8 +26154,8 @@
       <c r="F474" t="str">
         <v>Roof Mounted Solar PV System - 254 sq ft, 13x370W Modules, System Capacity: 4.81</v>
       </c>
-      <c r="G474" t="str">
-        <v xml:space="preserve"> 4.81</v>
+      <c r="G474">
+        <v>4.81</v>
       </c>
       <c r="H474" t="str">
         <v>Residential</v>
@@ -26264,8 +26264,8 @@
       <c r="F476" t="str">
         <v>Roof Mounted Solar PV System - 393 sq ft, 20x370W Modules, System Capacity: 7.4</v>
       </c>
-      <c r="G476" t="str">
-        <v xml:space="preserve"> 7.4</v>
+      <c r="G476">
+        <v>7.4</v>
       </c>
       <c r="H476" t="str">
         <v>Building Residential</v>
@@ -26427,8 +26427,8 @@
       <c r="F479" t="str">
         <v>Roof Mounted Solar PV System - 410 sq ft, 21x370W Modules, System Capacity: 7.77</v>
       </c>
-      <c r="G479" t="str">
-        <v xml:space="preserve"> 7.77</v>
+      <c r="G479">
+        <v>7.77</v>
       </c>
       <c r="H479" t="str">
         <v>Residential</v>
@@ -26481,8 +26481,8 @@
       <c r="F480" t="str">
         <v xml:space="preserve">Ground Mounted Solar PV System - 620 sq ft, 24x370W Modules, System Capacity: 8.88 </v>
       </c>
-      <c r="G480" t="str">
-        <v xml:space="preserve"> 8.88 </v>
+      <c r="G480">
+        <v>8.88</v>
       </c>
       <c r="H480" t="str">
         <v>Residential</v>
@@ -26756,8 +26756,8 @@
       <c r="F485" t="str">
         <v>Roof Mounted Solar PV System - 586 sq ft, 25x440W Modules, System Capacity: 11</v>
       </c>
-      <c r="G485" t="str">
-        <v xml:space="preserve"> 11</v>
+      <c r="G485">
+        <v>11</v>
       </c>
       <c r="H485" t="str">
         <v>Residential</v>
@@ -26810,8 +26810,8 @@
       <c r="F486" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 773 sq ft, 33x440W Modules, System Capacity: 14.52 </v>
       </c>
-      <c r="G486" t="str">
-        <v xml:space="preserve"> 14.52 </v>
+      <c r="G486">
+        <v>14.52</v>
       </c>
       <c r="H486" t="str">
         <v>Residential</v>
@@ -27137,8 +27137,8 @@
       <c r="F492" t="str">
         <v>Roof Mounted Solar PV System - 305 sq ft, 13x370W Modules, System Capacity: 4.81</v>
       </c>
-      <c r="G492" t="str">
-        <v xml:space="preserve"> 4.81</v>
+      <c r="G492">
+        <v>4.81</v>
       </c>
       <c r="H492" t="str">
         <v>Residential</v>
@@ -27353,8 +27353,8 @@
       <c r="F496" t="str">
         <v>Roof Mounted Solar PV System - 280 sq ft, 12x440W Modules, System Capacity: 5.28</v>
       </c>
-      <c r="G496" t="str">
-        <v xml:space="preserve"> 5.28</v>
+      <c r="G496">
+        <v>5.28</v>
       </c>
       <c r="H496" t="str">
         <v>Residential</v>
@@ -27623,8 +27623,8 @@
       <c r="F501" t="str">
         <v>Roof Mounted Solar PV System - 586 sq ft, 30x370W Modules, System Capacity: 11.1</v>
       </c>
-      <c r="G501" t="str">
-        <v xml:space="preserve"> 11.1</v>
+      <c r="G501">
+        <v>11.1</v>
       </c>
       <c r="H501" t="str">
         <v>Commercial</v>
@@ -28062,8 +28062,8 @@
       <c r="F509" t="str">
         <v>Roof Mounted Solar PV System - 451 sq ft 23x370W Modules, System Capacity: 8.51</v>
       </c>
-      <c r="G509" t="str">
-        <v xml:space="preserve"> 8.51</v>
+      <c r="G509">
+        <v>8.51</v>
       </c>
       <c r="H509" t="str">
         <v>Residential</v>
@@ -28170,8 +28170,8 @@
       <c r="F511" t="str">
         <v>Roof Mounted Solar PV System - 235 sq ft, 12x370W Modules, System Capacity: 4.44</v>
       </c>
-      <c r="G511" t="str">
-        <v xml:space="preserve"> 4.44</v>
+      <c r="G511">
+        <v>4.44</v>
       </c>
       <c r="H511" t="str">
         <v>Residential</v>
@@ -28224,8 +28224,8 @@
       <c r="F512" t="str">
         <v>Roof Mounted Solar PV System - 314 sq ft, 16x370W Modules, System Capacity: 5.92</v>
       </c>
-      <c r="G512" t="str">
-        <v xml:space="preserve"> 5.92</v>
+      <c r="G512">
+        <v>5.92</v>
       </c>
       <c r="H512" t="str">
         <v>Residential</v>
@@ -28767,8 +28767,8 @@
       <c r="F522" t="str">
         <v>Roof Mounted Solar PV System - 275sqft, 14x370W Modules, System Capacity: 5.18</v>
       </c>
-      <c r="G522" t="str">
-        <v xml:space="preserve"> 5.18</v>
+      <c r="G522">
+        <v>5.18</v>
       </c>
       <c r="H522" t="str">
         <v>Residential</v>
@@ -28929,8 +28929,8 @@
       <c r="F525" t="str">
         <v>Roof Mounted Solar PV System - 196sqft, 10x370W Modules, System Capacity: 3.7</v>
       </c>
-      <c r="G525" t="str">
-        <v xml:space="preserve"> 3.7</v>
+      <c r="G525">
+        <v>3.7</v>
       </c>
       <c r="H525" t="str">
         <v>Residential</v>
@@ -29309,7 +29309,7 @@
       <c r="F532" t="str">
         <v>PV Solar System 18 panels, 370W/panel; 19.66sqft/Panel; Total system area 354sqft; Total DC Output 6.66; Annual Output 9219h; Total AC Output 5.22</v>
       </c>
-      <c r="G532" t="str">
+      <c r="G532">
         <v>5.22</v>
       </c>
       <c r="H532" t="str">
@@ -29526,8 +29526,8 @@
       <c r="F536" t="str">
         <v xml:space="preserve">Roof Mounted Solar PV System - 5723.2 sq ft, 245 @ 440W Modules, System Capacity: 107.8 </v>
       </c>
-      <c r="G536" t="str">
-        <v xml:space="preserve"> 107.8 </v>
+      <c r="G536">
+        <v>107.8</v>
       </c>
       <c r="H536" t="str">
         <v>Building Commercial</v>
@@ -30186,7 +30186,7 @@
 Annual Output 5741h; _x000d_
 Total AC Output 3.48</v>
       </c>
-      <c r="G548" t="str">
+      <c r="G548">
         <v>3.48</v>
       </c>
       <c r="H548" t="str">
@@ -30407,8 +30407,8 @@
       <c r="F552" t="str">
         <v xml:space="preserve">PV Solar System: 10 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 208 sq ft; Total DC Output 4.2 ; Annual Output 6,090 h; Total AC Output 3.66 </v>
       </c>
-      <c r="G552" t="str">
-        <v xml:space="preserve">3.66 </v>
+      <c r="G552">
+        <v>3.66</v>
       </c>
       <c r="H552" t="str">
         <v>Residential</v>
@@ -30461,8 +30461,8 @@
       <c r="F553" t="str">
         <v xml:space="preserve">PV Solar System: 14 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 291.2 sq ft; Total DC Output 5.88 ; Annual Output 8,526 h; Total AC Output 5.04 </v>
       </c>
-      <c r="G553" t="str">
-        <v xml:space="preserve">5.04 </v>
+      <c r="G553">
+        <v>5.04</v>
       </c>
       <c r="H553" t="str">
         <v>Residential</v>
@@ -30569,7 +30569,7 @@
       <c r="F555" t="str">
         <v>PV Solar System 13 panels @ 370W/panel; 19.5sqft/panel; Total system area 255sqft;Total DC Output 4.81; Annual Output 5522h; Total AC Output 3.77</v>
       </c>
-      <c r="G555" t="str">
+      <c r="G555">
         <v>3.77</v>
       </c>
       <c r="H555" t="str">
@@ -30732,7 +30732,7 @@
       <c r="F558" t="str">
         <v>PV Solar System 14 panels @ 370W/panel; 19.5sqft/panel; Total system area 275sqft; Total DC Output 5.18; Annual Output 6659h; Total AC Output 4.06</v>
       </c>
-      <c r="G558" t="str">
+      <c r="G558">
         <v>4.06</v>
       </c>
       <c r="H558" t="str">
@@ -30841,8 +30841,8 @@
       <c r="F560" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 28 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 582.4 sq ft; Total DC Output 11.76 ; Annual Output 17,052 h; Total AC Output 10.08 </v>
       </c>
-      <c r="G560" t="str">
-        <v xml:space="preserve">10.08 </v>
+      <c r="G560">
+        <v>10.08</v>
       </c>
       <c r="H560" t="str">
         <v>Residential</v>
@@ -30951,8 +30951,8 @@
       <c r="F562" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 37 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 769.6 sq ft; Total DC Output 15.54 ; Annual Output 22,533 h; Total AC Output 13.32 </v>
       </c>
-      <c r="G562" t="str">
-        <v xml:space="preserve">13.32 </v>
+      <c r="G562">
+        <v>13.32</v>
       </c>
       <c r="H562" t="str">
         <v>Residential</v>
@@ -31005,8 +31005,8 @@
       <c r="F563" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 14 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 291.2 sq ft; Total DC Output 5.88 ; Annual Output 8,526 h; Total AC Output 5.04 </v>
       </c>
-      <c r="G563" t="str">
-        <v xml:space="preserve">5.04 </v>
+      <c r="G563">
+        <v>5.04</v>
       </c>
       <c r="H563" t="str">
         <v>Residential</v>
@@ -31059,8 +31059,8 @@
       <c r="F564" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 8 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 166.4 sq ft; Total DC Output 3.36 ; Annual Output 4,872 h; Total AC Output 2.88 </v>
       </c>
-      <c r="G564" t="str">
-        <v xml:space="preserve">2.88 </v>
+      <c r="G564">
+        <v>2.88</v>
       </c>
       <c r="H564" t="str">
         <v>Residential</v>
@@ -31113,8 +31113,8 @@
       <c r="F565" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 27 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 561.6 sq ft; Total DC Output 11.34 ; Annual Output 16,443 h; Total AC Output 9.72 </v>
       </c>
-      <c r="G565" t="str">
-        <v xml:space="preserve">9.72 </v>
+      <c r="G565">
+        <v>9.72</v>
       </c>
       <c r="H565" t="str">
         <v>Residential</v>
@@ -31222,8 +31222,8 @@
       <c r="F567" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 16 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 332.8 sq ft; Total DC Output 6.72 ; Annual Output 9,744 h; Total AC Output 5.76 </v>
       </c>
-      <c r="G567" t="str">
-        <v xml:space="preserve">5.76 </v>
+      <c r="G567">
+        <v>5.76</v>
       </c>
       <c r="H567" t="str">
         <v>Residential</v>
@@ -31738,8 +31738,8 @@
 Annual Output 17091 h;_x000d_
 Total AC Output 8.12 </v>
       </c>
-      <c r="G576" t="str">
-        <v xml:space="preserve">8.12 </v>
+      <c r="G576">
+        <v>8.12</v>
       </c>
       <c r="H576" t="str">
         <v>Commercial</v>
@@ -31849,7 +31849,7 @@
         <v xml:space="preserve">PV Solar System 12 panels @ 395W/panel; 21.07 sq ft/panel; Total system area 253 sq ft;_x000d_
 Total DC Output 4.74; Annual Output 7,056h; Total AC Output 4.6</v>
       </c>
-      <c r="G578" t="str">
+      <c r="G578">
         <v>4.6</v>
       </c>
       <c r="H578" t="str">
@@ -31903,8 +31903,8 @@
       <c r="F579" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 18 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 374.4 sq ft; Total DC Output 7.56 ; Annual Output 10,962 h; Total AC Output 6.48 </v>
       </c>
-      <c r="G579" t="str">
-        <v xml:space="preserve">6.48 </v>
+      <c r="G579">
+        <v>6.48</v>
       </c>
       <c r="H579" t="str">
         <v>Residential</v>
@@ -32071,7 +32071,7 @@
         <v xml:space="preserve">PV Solar System 16 panels @ 440W/Panel, 23.4 sqft/Panel, Total System Area 375sqft, Total DC Output 7.04,_x000d_
 Annual Output 10518 h, Total AC Output 4.64</v>
       </c>
-      <c r="G582" t="str">
+      <c r="G582">
         <v>4.64</v>
       </c>
       <c r="H582" t="str">
@@ -32406,8 +32406,8 @@
       <c r="F588" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 12 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 249.6 sq ft; Total DC Output 5.04 ; Annual Output 7,308 h; Total AC Output 4.32 </v>
       </c>
-      <c r="G588" t="str">
-        <v xml:space="preserve">4.32 </v>
+      <c r="G588">
+        <v>4.32</v>
       </c>
       <c r="H588" t="str">
         <v>Residential</v>
@@ -32460,7 +32460,7 @@
       <c r="F589" t="str">
         <v>PV Solar System 84 panels @ 410W/panel; 22.1 sq ft/panel; Total system area 1852 sq ft; Total DC Output 34.5; Annual Output 51140 h; Total AC Output 33.3</v>
       </c>
-      <c r="G589" t="str">
+      <c r="G589">
         <v>33.3</v>
       </c>
       <c r="H589" t="str">
@@ -33187,8 +33187,8 @@
       <c r="F602" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 10 panels @ 450W/panel; 22.4 sq ft/ panel; Total system area 224 sq ft; Total DC Output 4.5 ; Annual Output 6,525 h; Total AC Output 3.6 </v>
       </c>
-      <c r="G602" t="str">
-        <v xml:space="preserve">3.6 </v>
+      <c r="G602">
+        <v>3.6</v>
       </c>
       <c r="H602" t="str">
         <v>Residential</v>
@@ -33411,8 +33411,8 @@
       <c r="F606" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 23 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 478.4 sq ft; Total DC Output 9.66 ; Annual Output 14,007 h; Total AC Output 8.28 </v>
       </c>
-      <c r="G606" t="str">
-        <v xml:space="preserve">8.28 </v>
+      <c r="G606">
+        <v>8.28</v>
       </c>
       <c r="H606" t="str">
         <v>Residential</v>
@@ -33574,8 +33574,8 @@
       <c r="F609" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 12 panels @ 420W/panel; 20.8 sq ft/ panel; Total system area 249.6 sq ft; Total DC Output 5.04 ; Annual Output 7,308 h; Total AC Output 4.32 </v>
       </c>
-      <c r="G609" t="str">
-        <v xml:space="preserve">4.32 </v>
+      <c r="G609">
+        <v>4.32</v>
       </c>
       <c r="H609" t="str">
         <v>Residential</v>
@@ -34011,7 +34011,7 @@
       <c r="F617" t="str">
         <v>Solar PV System 43 panels @ 370W/Panel, 19sqft/Panel, Total System Area 843sqft, Total DC Output 15.91, Total AC Output 12.47</v>
       </c>
-      <c r="G617" t="str">
+      <c r="G617">
         <v>12.47</v>
       </c>
       <c r="H617" t="str">
@@ -34227,7 +34227,7 @@
       <c r="F621" t="str">
         <v>PV Solar System 24 panels @ 370W/panel; Total system area 471sqft; Total DC Output 8.88; Annual Output 11314h; Total AC Output 6.96</v>
       </c>
-      <c r="G621" t="str">
+      <c r="G621">
         <v>6.96</v>
       </c>
       <c r="H621" t="str">
@@ -35514,7 +35514,7 @@
 Annual Output 16564h;_x000d_
 Total AC Output 10.15</v>
       </c>
-      <c r="G644" t="str">
+      <c r="G644">
         <v>10.15</v>
       </c>
       <c r="H644" t="str">
@@ -35568,7 +35568,7 @@
       <c r="F645" t="str">
         <v>PV Solar System 16 panels @ 430 W/panel; 20.40 sq.ft./panel; Total System area 326.4 sq.ft.; Total DC Output 6.88 ; Annual Output 9,397 h; Total AC Output 5.91</v>
       </c>
-      <c r="G645" t="str">
+      <c r="G645">
         <v>5.91</v>
       </c>
       <c r="H645" t="str">
@@ -35840,7 +35840,7 @@
       <c r="F650" t="str">
         <v>PV Solar System 36 panels @ 430 W/panel; 20.40 sq.ft./panel; Total System area 734.40 sq.ft.; Total DC Output 15.48 ; Annual Output 21,261h; Total AC Output 13.31</v>
       </c>
-      <c r="G650" t="str">
+      <c r="G650">
         <v>13.31</v>
       </c>
       <c r="H650" t="str">
@@ -36285,7 +36285,7 @@
 Annual Output 2526h; _x000d_
 Total AC Output 14.79</v>
       </c>
-      <c r="G658" t="str">
+      <c r="G658">
         <v>14.79</v>
       </c>
       <c r="H658" t="str">
@@ -36666,7 +36666,7 @@
       <c r="F665" t="str">
         <v>PV Solar System 216 panels @ 430W/panel; 21sq ft/panel; Total system area 4536 sq ft; Total DC output 92.88 ; Annual Output 12,865 h; Total AC Output 77.09</v>
       </c>
-      <c r="G665" t="str">
+      <c r="G665">
         <v>77.09</v>
       </c>
       <c r="H665" t="str">
@@ -36781,8 +36781,8 @@
 ?	Annual Output 5,274 h_x000d__x000d_
 ?	Total AC Output 3.255 </v>
       </c>
-      <c r="G667" t="str">
-        <v xml:space="preserve">3.255 </v>
+      <c r="G667">
+        <v>3.255</v>
       </c>
       <c r="H667" t="str">
         <v>Residential</v>
@@ -36890,8 +36890,8 @@
       <c r="F669" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 13 panels @ 450W/panel; 22.4 sq ft/ panel; Total system area 291.2 sq ft; Total DC Output 5.85 ; Annual Output 8,482 h; Total AC Output 5.03 </v>
       </c>
-      <c r="G669" t="str">
-        <v xml:space="preserve">5.03 </v>
+      <c r="G669">
+        <v>5.03</v>
       </c>
       <c r="H669" t="str">
         <v>Residential</v>
@@ -37115,7 +37115,7 @@
       <c r="F673" t="str">
         <v>Car Park Pergola &amp; PV Solar System 38 panels @ 370W/panel; Total system area 746sqft; Total DC Output 14.06; Annual Output 17557h; Total AC Output 11.02</v>
       </c>
-      <c r="G673" t="str">
+      <c r="G673">
         <v>11.02</v>
       </c>
       <c r="H673" t="str">
@@ -37941,7 +37941,7 @@
         <v xml:space="preserve">Roof Top PV Solar System, 33 Panels @435W/panel; 21.1 sq ft/panel; Total system area 730 sq. ft.;_x000d_
 Total DC Output 14.4; Annual Output 22,361h; Total AC Output 13.97</v>
       </c>
-      <c r="G688" t="str">
+      <c r="G688">
         <v>13.97</v>
       </c>
       <c r="H688" t="str">
@@ -37995,8 +37995,8 @@
       <c r="F689" t="str">
         <v xml:space="preserve">Proposed roof mounted PV Solar System 40 panels @ 430 W/panel; 21.50 sq ft/ panel; Total system area 860 sq ft; DC Output 17.20 ; Annual Output 23,494h; Total AC Output 14.79 </v>
       </c>
-      <c r="G689" t="str">
-        <v xml:space="preserve">14.79 </v>
+      <c r="G689">
+        <v>14.79</v>
       </c>
       <c r="H689" t="str">
         <v>Building Commercial</v>
@@ -38761,7 +38761,7 @@
       <c r="F703" t="str">
         <v>PV Solar System 6 panels @ 430 W/panel; 20.40 sq.ft./panel; Total System area 122.40 sq.ft.; Total DC Output 2.58 ; Annual Output 3,343h; Total AC Output 2.21</v>
       </c>
-      <c r="G703" t="str">
+      <c r="G703">
         <v>2.21</v>
       </c>
       <c r="H703" t="str">
@@ -39252,8 +39252,8 @@
       <c r="F712" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 18 panels @ 440W/panel; 20.9 sq ft/ panel; Total system area 376.2 sq ft; Total DC Output 7.92 ; Annual Output 11,484 h; Total AC Output 6.14 </v>
       </c>
-      <c r="G712" t="str">
-        <v xml:space="preserve">6.14 </v>
+      <c r="G712">
+        <v>6.14</v>
       </c>
       <c r="H712" t="str">
         <v>Residential</v>
@@ -39307,7 +39307,7 @@
         <v xml:space="preserve">PV Solar System 19 panels @ 370W/panel; 19.6sqft/panel. Total system area sqft; _x000d_
 Total DC Output 7.03; Annual Output 9691h; Total AC Output 5.51</v>
       </c>
-      <c r="G713" t="str">
+      <c r="G713">
         <v>5.51</v>
       </c>
       <c r="H713" t="str">
@@ -39415,7 +39415,7 @@
       <c r="F715" t="str">
         <v>PV Solar System 10 panels @ 410W/panel; 22.1 sq ft/panel; Total system area 221 sq ft; Total DC Output 4.10; Annual Output 6,378h; Total AC Output 3</v>
       </c>
-      <c r="G715" t="str">
+      <c r="G715">
         <v>3</v>
       </c>
       <c r="H715" t="str">
@@ -39469,7 +39469,7 @@
       <c r="F716" t="str">
         <v>PV Solar System 14 panels @ 410W/panel; 22.1 sq ft/panel; Total system area 310 sq ft; Total DC Output 5.70; Annual Output 7,044h; Total AC Output 4.2</v>
       </c>
-      <c r="G716" t="str">
+      <c r="G716">
         <v>4.2</v>
       </c>
       <c r="H716" t="str">
@@ -39962,7 +39962,7 @@
 Annual Output 17529h; _x000d_
 Total AC Output 10.44</v>
       </c>
-      <c r="G725" t="str">
+      <c r="G725">
         <v>10.44</v>
       </c>
       <c r="H725" t="str">
@@ -40451,7 +40451,7 @@
       <c r="F734" t="str">
         <v>NEW PV Solar System 2 panels @ 400 W/panel; 19 sq.ft./panel; Total System area 38 sq.ft.; Total DC Output 0.79 ; Annual Output 1,024h; Total AC Output 0.67.</v>
       </c>
-      <c r="G734" t="str">
+      <c r="G734">
         <v>0.67</v>
       </c>
       <c r="H734" t="str">
@@ -41169,7 +41169,7 @@
       <c r="F747" t="str">
         <v>PV Solar System 10 panels @ 430 W/panel; 20.40 sq.ft./panel; Total System area 204 sq.ft.; Total DC Output 4.30 ; Annual Output 5,571h; Total AC Output 3.69.</v>
       </c>
-      <c r="G747" t="str">
+      <c r="G747">
         <v>3.69</v>
       </c>
       <c r="H747" t="str">
@@ -41558,8 +41558,8 @@
       <c r="F754" t="str">
         <v xml:space="preserve">Proposed Asphalt Plant, Aggregate Screening Plant, New Workshop, Lab, Two Container Office Structures, and Site Services, Decommissioning and Removal of Existing Asphalt Plant, Proposed New 8 Ft High Chain Link Fence and Double Sliding Gate, Regraded Portion of Land, Demolition of Specified Buildings and Structures, Asphalt Plant Access Road, Cold Feed Bins, Ramps, Sorted Aggregate Bunkers and 115 Roof Mounted Solar PV Solar System 115 panels @ 405W/panel; 21.496 sq ft/ panel; Total system area 2,472.04 sq ft; Total DC Output 46.575 ; Annual Output 76,919 h; Total AC Output 58.00 </v>
       </c>
-      <c r="G754" t="str">
-        <v xml:space="preserve">58.00 </v>
+      <c r="G754">
+        <v>58</v>
       </c>
       <c r="H754" t="str">
         <v>Building Commercial</v>
@@ -41889,7 +41889,7 @@
       <c r="F760" t="str">
         <v>PV Solar System 40 panels @ 430 W/panel; 20.40 sq.ft./panel; Total System area 816 sq.ft.; Total DC Output 17.20 ; Annual Output 22,286h; Total AC Output 14.79.</v>
       </c>
-      <c r="G760" t="str">
+      <c r="G760">
         <v>14.79</v>
       </c>
       <c r="H760" t="str">
@@ -42601,8 +42601,8 @@
       <c r="F773" t="str">
         <v xml:space="preserve">Roof-mounted PV Solar System: 33 panels @ 440W/panel; 20.9 sq ft/ panel; Total system area 693 sq ft; Total DC Output 14.52 ; Annual Output 21,054 h; Total AC Output 15.68 </v>
       </c>
-      <c r="G773" t="str">
-        <v xml:space="preserve">15.68 </v>
+      <c r="G773">
+        <v>15.68</v>
       </c>
       <c r="H773" t="str">
         <v>Residential</v>
